--- a/data-vh/Неделя_18.05-24.05_2026_ВХ.xlsx
+++ b/data-vh/Неделя_18.05-24.05_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$8</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,577 +562,629 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="82.05" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000070</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>19.05.2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000205 от 18.05.2026 15:11:01</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="8" t="n">
         <v>243.6</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Р-р 746-2 фактически 743 – 746 мм (недостаток длины связующего элемента компенсирован наплавлением металла). Выступание связующих элементов по СТО не более 1,5мм, фактически до 4мм. Занижение обрамляющего элемента по СТО не более 1мм, фактически до 4мм. Выступание обрамляющего элемента по СТО не более 1мм, фактически до 4мм. Выгнутость по СТО не более 3мм, фактически до 5мм. Механические повреждения. Дефекты сварных швов: брызги металла, кратеры, поры, натёки, прожоги, несплавления.</t>
         </is>
       </c>
+      <c r="Q2" s="7" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="34.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000071</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>20.05.2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002037 от 19.05.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>МЕТИЗКОМПЛЕКТ ПК ООО(ЭДО Такском ЗП согл. от 01.04.2026)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>БЕЗ МАРКИРОВКИ_ГПЦ(закупка) Болт М16-6azx60.58.0940 ГОСТ 7802-81 Оцинкованное</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>Метизы</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="12" t="n">
         <v>1900</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="8" t="n">
         <v>229.9</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Отсутствует маркировка класса прочности. Диаметр головки по ГОСТ7802  35+-0.8мм, фактически 37,28-37,96мм. Высота головки по ГОСТ 7802 8+-0,45мм, фактически 10мм. Неполный профиль резьбы.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>Письмо Снегирев</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="22.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000071</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>20.05.2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-002037 от 19.05.2026 23:59:59</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>МЕТИЗКОМПЛЕКТ ПК ООО(ЭДО Такском ЗП согл. от 01.04.2026)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Склад готовой продукции</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>ГПЦ(закупка) (в ШТ) Гайка М16-6H.6.0930 ГОСТ 5915-70 Оцинкованное</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Метизы</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Высота гайки по ГОСТ 5915 14,8-1,1мм, фактически 12,84-12,99мм.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>Письмо Снегирев</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="34.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000072</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>22.05.2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000221 от 21.05.2026 16:47:49</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="14" t="n">
         <v>6990.4</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ:    Не выполнено требование "Заварить"         Дефекты сварных швов:    брызги металла, подрезы, шлак, несплавление.        Дефекты лазерной резки: незавершенный рез, налипший шлак.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="22.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000073</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>22.05.2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000223 от 22.05.2026 13:04:19</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="14" t="n">
         <v>3495.2</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>ЭЗ 248.00.00.000 СБ:Не выполнено требование "Заварить". Дефекты сварных швов: брызги металла, подрезы, шлак, несплавление, остатки сварочной проволоки.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="22.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000074</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>23.05.2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000225 от 23.05.2026 8:39:12</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Опора МСО-ФГ-7-9-01 СТО 07525912-300-2021 (ФГС-700-9,0-01) (ОО 345.00.00.000 СБ)  (от п</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="10" t="n">
         <v>3890.25</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Брызги металла. Несплавления. Остатки сварочной проволоки.</t>
         </is>
       </c>
+      <c r="Q7" s="7" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="58.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000075</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>23.05.2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000226 от 23.05.2026 12:44:03</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="10" t="n">
         <v>1546.95</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Малозначительное Неустранимое</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Размер 2380+-2мм, фактически 2384мм (1шт). Размер кромки 100+1мм, фактически 199мм. Размер до тех. отверстия 35+-1мм, фактически 30мм (2шт). Размер между тех. отверстиями 770+-1мм, фактически 770мм, 685мм, 871мм (2шт). Размер кромки 15+-1мм, фактически 13-15мм Отсутствует кромка 20+-0,3*3+-1.Размер 55+-0,4мм, фактически 53,69-56,81мм. Заусенцы. Остатки силиконового герметика..</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников ОЭУ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q8">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>